--- a/New_FacetMeanStress/Data_Files/APSlideTether/4NP_APSlide_Tether_CMS.xlsx
+++ b/New_FacetMeanStress/Data_Files/APSlideTether/4NP_APSlide_Tether_CMS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sjturner.FORTLEWIS\OneDrive - Fort Lewis College\Disc\FCMS results\APSlideTether\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brburrough\Repo_Git\Spinal-Disc-Replacement-Code\New_FacetMeanStress\Data_Files\APSlideTether\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{0742FD0B-4179-4CDA-883C-DAE76E041543}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{6124133F-D72D-42E0-95E9-F6195664C302}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{0742FD0B-4179-4CDA-883C-DAE76E041543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6124133F-D72D-42E0-95E9-F6195664C302}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9024" xr2:uid="{F634B659-747B-4905-BAD5-FBF6DC1E7B9B}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{F634B659-747B-4905-BAD5-FBF6DC1E7B9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,12 +128,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,9 +536,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -577,7 +576,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -683,7 +682,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -825,7 +824,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -834,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F87810A-1AEA-4D38-B2C9-5BDD381D366E}">
   <dimension ref="A1:AN58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -849,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
         <v>1</v>
       </c>
@@ -857,7 +856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -883,7 +882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1005,7 +1004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1143,7 +1142,7 @@
         <v>0.23133662282548292</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2.0512600000000001</v>
       </c>
@@ -1281,7 +1280,7 @@
         <v>0.24975948658362579</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2.1153300000000002</v>
       </c>
@@ -1419,7 +1418,7 @@
         <v>0.27651968065018601</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2.16533</v>
       </c>
@@ -1557,7 +1556,7 @@
         <v>0.3106760881320747</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2.2246999999999999</v>
       </c>
@@ -1695,7 +1694,7 @@
         <v>0.34493154339627219</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2.2668900000000001</v>
       </c>
@@ -1833,7 +1832,7 @@
         <v>0.39043309395586073</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2.3262700000000001</v>
       </c>
@@ -1971,7 +1970,7 @@
         <v>0.43886569164874895</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2.3684599999999998</v>
       </c>
@@ -2109,7 +2108,7 @@
         <v>0.4803903778720483</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2.4278300000000002</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>0.52397394088778904</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2.4542000000000002</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>0.5780554287285381</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2.5061499999999999</v>
       </c>
@@ -2523,7 +2522,7 @@
         <v>0.62066649270418839</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2.5507599999999999</v>
       </c>
@@ -2661,7 +2660,7 @@
         <v>0.66952229255461138</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2.60453</v>
       </c>
@@ -2799,7 +2798,7 @@
         <v>0.7112257688530067</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2.65273</v>
       </c>
@@ -2937,7 +2936,7 @@
         <v>0.76983348402845186</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2.7006199999999998</v>
       </c>
@@ -3075,7 +3074,7 @@
         <v>0.82088179806564887</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2.75176</v>
       </c>
@@ -3213,7 +3212,7 @@
         <v>0.87566472132948137</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2.80444</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>0.92522716811733619</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2.8583699999999999</v>
       </c>
@@ -3489,7 +3488,7 @@
         <v>0.97492131299337426</v>
       </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2.9134199999999999</v>
       </c>
@@ -3627,7 +3626,7 @@
         <v>1.0374254655715414</v>
       </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2.9619599999999999</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>1.0929524282373231</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
@@ -3903,7 +3902,7 @@
         <v>1.1339547953797584</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -3911,7 +3910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -3922,7 +3921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -3948,7 +3947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -4070,7 +4069,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2</v>
       </c>
@@ -4197,7 +4196,7 @@
         <f>(Table817[[#This Row],[time]]-2)*2</f>
         <v>0</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AL38">
         <v>83.133399999999995</v>
       </c>
       <c r="AM38">
@@ -4208,7 +4207,7 @@
         <v>0.23133662282548292</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2.0512600000000001</v>
       </c>
@@ -4346,7 +4345,7 @@
         <v>0.21509274792464805</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2.1153300000000002</v>
       </c>
@@ -4484,7 +4483,7 @@
         <v>0.19644163450722299</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2.16533</v>
       </c>
@@ -4622,7 +4621,7 @@
         <v>0.18300767056440362</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2.2246999999999999</v>
       </c>
@@ -4760,7 +4759,7 @@
         <v>0.16989673035200567</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2.2668900000000001</v>
       </c>
@@ -4898,7 +4897,7 @@
         <v>0.16059596143610846</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2.3262700000000001</v>
       </c>
@@ -5036,7 +5035,7 @@
         <v>0.15100268722315122</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2.3684599999999998</v>
       </c>
@@ -5174,7 +5173,7 @@
         <v>0.14271948239666862</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2.4278300000000002</v>
       </c>
@@ -5312,7 +5311,7 @@
         <v>0.13395186631117881</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2.4542000000000002</v>
       </c>
@@ -5450,7 +5449,7 @@
         <v>0.1297319245868962</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2.5061499999999999</v>
       </c>
@@ -5588,7 +5587,7 @@
         <v>0.12023627027432651</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2.5507599999999999</v>
       </c>
@@ -5726,7 +5725,7 @@
         <v>0.11063013940209264</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2.60453</v>
       </c>
@@ -5864,7 +5863,7 @@
         <v>0.10245534169833964</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2.65273</v>
       </c>
@@ -6002,7 +6001,7 @@
         <v>9.6678954895673422E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2.7006199999999998</v>
       </c>
@@ -6140,7 +6139,7 @@
         <v>8.9826292055890516E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2.75176</v>
       </c>
@@ -6278,7 +6277,7 @@
         <v>8.1454977131355299E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2.80444</v>
       </c>
@@ -6416,7 +6415,7 @@
         <v>7.6549055882596098E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2.8583699999999999</v>
       </c>
@@ -6554,7 +6553,7 @@
         <v>7.0326736047773106E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2.9134199999999999</v>
       </c>
@@ -6692,7 +6691,7 @@
         <v>6.3961543916328328E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2.9619599999999999</v>
       </c>
@@ -6830,7 +6829,7 @@
         <v>5.766929729105074E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>3</v>
       </c>
@@ -7210,18 +7209,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7244,18 +7243,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F766EBCA-0B73-4393-AD3D-9349BE896360}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE04123E-BF64-43B8-8D56-43BFD77755A8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F766EBCA-0B73-4393-AD3D-9349BE896360}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>